--- a/Oak Project/Data/Survival_HeightOct2025Clean.xlsx
+++ b/Oak Project/Data/Survival_HeightOct2025Clean.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cagiudic\Documents\AdvancedQuantF26\Oak Project\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42A2F704-9329-4997-BADC-F12C13D15822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CF37BA6-1D3B-46EC-86CF-A4F248D4E645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7335" yWindow="2475" windowWidth="21600" windowHeight="12375" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5865" yWindow="2460" windowWidth="21600" windowHeight="12375" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Instructions" sheetId="1" r:id="rId1"/>
@@ -69,6 +69,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -89,6 +90,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -110,6 +112,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -127,6 +130,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -144,6 +148,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -161,6 +166,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -178,6 +184,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -195,6 +202,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -212,6 +220,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -229,6 +238,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -246,6 +256,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -263,6 +274,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -280,6 +292,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -297,6 +310,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -314,6 +328,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -331,6 +346,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -348,6 +364,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -365,6 +382,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -382,6 +400,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -409,6 +428,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="Arial"/>
+            <family val="2"/>
             <scheme val="minor"/>
           </rPr>
           <t xml:space="preserve">[Threaded comment]
@@ -427,7 +447,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="127">
   <si>
     <t>Don't edit column K</t>
   </si>
@@ -803,12 +823,18 @@
   <si>
     <t>Oak_type</t>
   </si>
+  <si>
+    <t>Seedling_Ht</t>
+  </si>
+  <si>
+    <t>Num_leaves</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -834,6 +860,13 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="4">
@@ -1407,10 +1440,10 @@
         <v>14</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>15</v>
+        <v>125</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>17</v>
+        <v>126</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>18</v>
@@ -17581,11 +17614,11 @@
       </c>
       <c r="H1" s="9" t="str">
         <f>IF(Input1!H1=Input2!H1, Input1!H1, "ERROR")</f>
-        <v>Seedling Height</v>
+        <v>ERROR</v>
       </c>
       <c r="I1" s="9" t="str">
         <f>IF(Input1!I1=Input2!I1, Input1!I1, "ERROR")</f>
-        <v># of Leaves on Seedlings</v>
+        <v>ERROR</v>
       </c>
       <c r="J1" s="9" t="str">
         <f>IF(Input1!J1=Input2!J1, Input1!J1, "ERROR")</f>
